--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EgvyJSJo</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AaLVdEGK</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -669,18 +669,18 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>SOLVXEbk</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">letexier f 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>0js8u60b</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>EgvyJSJo</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>jqSiuc6F</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>SIFtcwDc</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EgvyJSJo</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>fHYrsJy3</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">brisard j 
   fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>ripawyyS</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>zuUcoUwO</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>2NocJFqd</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AaLVdEGK</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>M5VGwpVA</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>AaLVdEGK</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>6ehlLyFq</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>zkPwWhT1</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -669,18 +669,252 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SIFtcwDc</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rainville n 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>KYsw3uKl</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,240 +684,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CKcVGr7E</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">batta f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>lb31RXzP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>pSpI7vU0</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lissorgue r 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rainville n 
-  fra </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>h89kUbu5</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>KAwSWnoE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ppvl45N8</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">leonard t 
-  fra </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>KYsw3uKl</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>EgvyJSJo</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,6 +684,214 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>ppvl45N8</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pSpI7vU0</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CKcVGr7E</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>lb31RXzP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KQAqguF7</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>KYsw3uKl</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>OCd990al</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>ObHze1pe</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rainville n 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>h89kUbu5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8nivFMyR</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>KAwSWnoE</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>SOLVXEbk</t>
+          <t>ppvl45N8</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0js8u60b</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EgvyJSJo</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>jqSiuc6F</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fHYrsJy3</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,7 +539,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
+          <t xml:space="preserve">delajod w 
   fra </t>
         </is>
       </c>
@@ -550,14 +550,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ripawyyS</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +565,25 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>zuUcoUwO</t>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>2NocJFqd</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M5VGwpVA</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AaLVdEGK</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6ehlLyFq</t>
+          <t>xrJSdNFr</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zkPwWhT1</t>
+          <t>hhlQ5IbD</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -669,25 +669,25 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">letexier f 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SIFtcwDc</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -695,25 +695,25 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -721,25 +721,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -747,25 +747,25 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
+          <t xml:space="preserve">stinat j 
   fra </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>lb31RXzP</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -773,25 +773,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">bastien b 
   fra </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KYsw3uKl</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EgvyJSJo</t>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -799,25 +799,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">leonard t 
   fra </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -825,25 +825,25 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">rainville n 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>h89kUbu5</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -851,25 +851,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
+          <t xml:space="preserve">lissorgue r 
   fra </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KAwSWnoE</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -877,18 +877,44 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">millot b 
   fra </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>YHU1oFVQ</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ppvl45N8</t>
+          <t>pSpI7vU0</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>CKcVGr7E</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
-  fra </t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>KQAqguF7</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,406 +496,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
-  fra </t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>KQAqguF7</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>OCd990al</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ObHze1pe</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lissorgue r 
-  fra </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8nivFMyR</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>xrJSdNFr</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hhlQ5IbD</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wattellier e 
-  fra </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>vmgpBDzg</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bk9o9i55</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">turpin c 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6FCg7VZH</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>tYQyK8JN</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">leonard t 
-  fra </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lissorgue r 
-  fra </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lissorgue r 
-  fra </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
         <is>
           <t>8MdrBIUb</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,60 +453,339 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pSpI7vU0</t>
+          <t>OCd990al</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CKcVGr7E</t>
+          <t>ObHze1pe</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KQAqguF7</t>
+          <t>8nivFMyR</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>xrJSdNFr</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hhlQ5IbD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vmgpBDzg</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bk9o9i55</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>6FCg7VZH</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tYQyK8JN</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IgtCPCkn</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SU02594U</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ChZKNjKb</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>p6XSLUlB</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6ZfxDZ5t</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,112 +453,137 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>OCd990al</t>
+          <t>vmgpBDzg</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ObHze1pe</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>8nivFMyR</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xrJSdNFr</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hhlQ5IbD</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -566,25 +591,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">vernice m 
+          <t xml:space="preserve">dechepy b 
   fra </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -592,25 +617,25 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">turpin c 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -618,25 +643,25 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
+          <t xml:space="preserve">wattellier e 
   fra </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -644,146 +669,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">bollengier m 
   fra </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IgtCPCkn</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">leonard t 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>SU02594U</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lissorgue r 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lissorgue r 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
         <is>
           <t>vVQcGxl1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
+          <t xml:space="preserve">ben el hadj salem h 
   fra </t>
         </is>
       </c>
@@ -550,7 +550,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vmgpBDzg</t>
+          <t>bk9o9i55</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
-  fra </t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>6FCg7VZH</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
-  fra </t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>tYQyK8JN</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
+          <t>0tIbS515</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,25 +536,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -591,25 +556,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
-  fra </t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -617,25 +576,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -643,42 +596,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">wattellier e 
-  fra </t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
         <is>
           <t>vVQcGxl1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bk9o9i55</t>
+          <t>IgtCPCkn</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
+          <t>0tIbS515</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>6FCg7VZH</t>
+          <t>SU02594U</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>tYQyK8JN</t>
+          <t>ChZKNjKb</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>p6XSLUlB</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>pYizckpN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>6ZfxDZ5t</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -540,66 +540,6 @@
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>ChZKNjKb</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p6XSLUlB</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZfxDZ5t</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
         <is>
           <t>vVQcGxl1</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IgtCPCkn</t>
+          <t>vsYzkTIc</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t xml:space="preserve">bastien b 
+  fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SU02594U</t>
+          <t>0dMqm7mA</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t xml:space="preserve">stinat j 
+  fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ChZKNjKb</t>
+          <t>CGH7Enso</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t xml:space="preserve">delajod w 
+  fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>p6XSLUlB</t>
+          <t>8MPiooIM</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t xml:space="preserve">angoula g 
+  fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6ZfxDZ5t</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,12 +565,122 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t xml:space="preserve">millot b 
+  fra </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>M51AY7YG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>E3tkRPQj</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>fJaIWo3T</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Qw81zU34</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,6 +684,240 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0K4Ww3Ad</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fiy8wfGD</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>noOg1c8K</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>v39B1623</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>6V4QeyWs</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vsYzkTIc</t>
+          <t>hCffxjZi</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -461,25 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>0dMqm7mA</t>
+          <t>M51AY7YG</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -487,25 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CGH7Enso</t>
+          <t>E3tkRPQj</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -513,25 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MPiooIM</t>
+          <t>fJaIWo3T</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -539,25 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>Qw81zU34</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -565,356 +536,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>M51AY7YG</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>E3tkRPQj</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>fJaIWo3T</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Qw81zU34</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">leonard t 
-  fra </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>4fMAHvLm</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0K4Ww3Ad</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>fiy8wfGD</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">leonard t 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>noOg1c8K</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>v39B1623</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>6V4QeyWs</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>6HPisxHl</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>nTCJapXF</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frappart s 
-  fra </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>EsTauGo1</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frappart s 
-  fra </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,27 +453,28 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>0K4Ww3Ad</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,72 +482,399 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6HPisxHl</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>nTCJapXF</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>EsTauGo1</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>CWxpUrtf</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>S66OuPup</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MRfkjXaJ</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>zBdshgV6</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>v3PZcqJP</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>xb7MlutC</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>lxyu7Met</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
         <is>
           <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,28 +448,27 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0K4Ww3Ad</t>
+          <t>fiy8wfGD</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fiy8wfGD</t>
+          <t>noOg1c8K</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -482,397 +476,130 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>noOg1c8K</t>
+          <t>v39B1623</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
+          <t>0tIbS515</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>v39B1623</t>
+          <t>6V4QeyWs</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>6V4QeyWs</t>
+          <t>6HPisxHl</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6HPisxHl</t>
+          <t>nTCJapXF</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nTCJapXF</t>
+          <t>EsTauGo1</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>EsTauGo1</t>
+          <t>S66OuPup</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>S66OuPup</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>MRfkjXaJ</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">turpin c 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>zBdshgV6</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>v3PZcqJP</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>xb7MlutC</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">letexier f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dechepy b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">letexier f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
         <is>
           <t>d0X3cO3I</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hCffxjZi</t>
+          <t>MRfkjXaJ</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +461,25 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t xml:space="preserve">batta f 
+  fra </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>M51AY7YG</t>
+          <t>zBdshgV6</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +487,25 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t xml:space="preserve">stinat j 
+  fra </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>E3tkRPQj</t>
+          <t>v3PZcqJP</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +513,25 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t xml:space="preserve">leonard t 
+  fra </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>fJaIWo3T</t>
+          <t>xb7MlutC</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +539,25 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t xml:space="preserve">brisard j 
+  fra </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Qw81zU34</t>
+          <t>lxyu7Met</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,12 +565,356 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>CWxpUrtf</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bDeVnJAO</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>p4Um50Qh</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>zZA5hNtm</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ee8YgF0f</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xYNVFHvB</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z9REJaun</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Wf14adfU</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8Kp3c9Oq</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -461,16 +456,10 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">batta f 
-  fra </t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>UapruDaf</t>
         </is>
@@ -487,16 +476,10 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>K6b7RoBp</t>
         </is>
@@ -513,16 +496,10 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
-  fra </t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>tAufB9Mi</t>
         </is>
@@ -539,16 +516,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">brisard j 
-  fra </t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>4fMAHvLm</t>
         </is>
@@ -565,16 +536,10 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>OpNm82MB</t>
         </is>
@@ -591,16 +556,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>pYizckpN</t>
         </is>
@@ -617,16 +576,10 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>8MdrBIUb</t>
         </is>
@@ -643,16 +596,10 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">leonard t 
-  fra </t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>tAufB9Mi</t>
         </is>
@@ -669,252 +616,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>pYizckpN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>xYNVFHvB</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>z9REJaun</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Wf14adfU</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">batta f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8Kp3c9Oq</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frappart s 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>IHSe3ve5</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>rZUMHwAb</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">frappart s 
-  fra </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WhWcJjo3</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>4nvCemgd</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>OUcd1IPH</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MRfkjXaJ</t>
+          <t>bDeVnJAO</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zBdshgV6</t>
+          <t>p4Um50Qh</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>v3PZcqJP</t>
+          <t>zZA5hNtm</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,7 +496,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -508,7 +508,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>xb7MlutC</t>
+          <t>Ee8YgF0f</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,110 +516,10 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>lxyu7Met</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>bDeVnJAO</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>p4Um50Qh</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>zZA5hNtm</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ee8YgF0f</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
         <is>
           <t>pYizckpN</t>
         </is>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,80 +453,215 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDeVnJAO</t>
+          <t>xYNVFHvB</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pYizckpN</t>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p4Um50Qh</t>
+          <t>z9REJaun</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zZA5hNtm</t>
+          <t>Wf14adfU</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Ee8YgF0f</t>
+          <t>8Kp3c9Oq</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>IHSe3ve5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>rZUMHwAb</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>nVS1TlC4</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WhWcJjo3</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>4nvCemgd</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OUcd1IPH</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>vwbmU7aL</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>xYNVFHvB</t>
+          <t>IHSe3ve5</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,19 +462,19 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>UapruDaf</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>z9REJaun</t>
+          <t>rZUMHwAb</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,19 +483,19 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Wf14adfU</t>
+          <t>WhWcJjo3</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -504,19 +504,19 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8Kp3c9Oq</t>
+          <t>4nvCemgd</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -525,19 +525,19 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>4fMAHvLm</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>OUcd1IPH</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -546,70 +546,85 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -621,28 +636,33 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -650,18 +670,122 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">dechepy b 
+          <t xml:space="preserve">angoula g 
   fra </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>h8K6HUFF</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wattellier e 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>CWxpUrtf</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHSe3ve5</t>
+          <t>vwbmU7aL</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -462,19 +462,19 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rZUMHwAb</t>
+          <t>WzwSMPie</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,19 +483,19 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WhWcJjo3</t>
+          <t>OAZJOoNr</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -504,19 +504,19 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>4nvCemgd</t>
+          <t>S2WzL3M7</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -525,19 +525,19 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>OUcd1IPH</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -546,227 +546,207 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WMcg8Qx2</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>vPIEF8pS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nVutWTU8</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>lYpTkOLs</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>p0vxl2jf</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>hQspntL6</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millot b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>vaZNtoqR</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t xml:space="preserve">turpin c 
   fra </t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>UapruDaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>WzwSMPie</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>OAZJOoNr</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">letexier f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>S2WzL3M7</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>b9aoAn8k</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wattellier e 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">letexier f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lissorgue r 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -774,18 +754,122 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">lissorgue r 
+          <t xml:space="preserve">vernice m 
   fra </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>CWxpUrtf</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -453,423 +448,100 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>vwbmU7aL</t>
+          <t>b9aoAn8k</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WzwSMPie</t>
+          <t>h8K6HUFF</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OAZJOoNr</t>
+          <t>WMcg8Qx2</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
+          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>S2WzL3M7</t>
+          <t>vPIEF8pS</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>nVutWTU8</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>h8K6HUFF</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>WMcg8Qx2</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>vPIEF8pS</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
           <t>6FKPxxgf</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>nVutWTU8</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>lYpTkOLs</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>p0vxl2jf</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>hQspntL6</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millot b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>vaZNtoqR</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">turpin c 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>WdE2Z2y1</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vernice m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>vNHAXt6D</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">turpin c 
-  fra </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>KdJMr7EE</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">leonard t 
-  fra </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>h2acepbK</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>AsQgyP6l</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brisard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,100 +453,428 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>b9aoAn8k</t>
+          <t>lYpTkOLs</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>0tIbS515</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>h8K6HUFF</t>
+          <t>p0vxl2jf</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WMcg8Qx2</t>
+          <t>hQspntL6</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8MdrBIUb</t>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vPIEF8pS</t>
+          <t>vaZNtoqR</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>nVS1TlC4</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>nVutWTU8</t>
+          <t>WdE2Z2y1</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>25Wk0Fko</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>vNHAXt6D</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>6FKPxxgf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>KdJMr7EE</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h2acepbK</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AsQgyP6l</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>0ljCkFRb</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">delajod w 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>bqYbtBlo</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kherradji a 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>rX720WuH</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lissorgue r 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>n5Eg2hB4</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">angoula g 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>vuBo4Eth</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>4Md3iycn</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">batta f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>EuWhpKkJ</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Y1lKmgdB</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>UTsToXQN</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -459,13 +454,12 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>YHU1oFVQ</t>
         </is>
@@ -480,13 +474,12 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>K6b7RoBp</t>
         </is>
@@ -501,13 +494,12 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>pCcFFE7M</t>
         </is>
@@ -522,13 +514,12 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>nVS1TlC4</t>
         </is>
@@ -543,13 +534,12 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>25Wk0Fko</t>
         </is>
@@ -566,16 +556,10 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
+          <t>vVQcGxl1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>6FKPxxgf</t>
         </is>
@@ -590,13 +574,12 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>nVS1TlC4</t>
         </is>
@@ -611,13 +594,12 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>d0X3cO3I</t>
         </is>
@@ -632,249 +614,14 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>vVQcGxl1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>4fMAHvLm</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>0ljCkFRb</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">delajod w 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>bqYbtBlo</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kherradji a 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>rX720WuH</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lissorgue r 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>n5Eg2hB4</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">angoula g 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>vuBo4Eth</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>4Md3iycn</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">batta f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>EuWhpKkJ</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dechepy b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Y1lKmgdB</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">turpin c 
-  fra </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>UTsToXQN</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">turpin c 
-  fra </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -448,180 +453,423 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>lYpTkOLs</t>
+          <t>0ljCkFRb</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>p0vxl2jf</t>
+          <t>bqYbtBlo</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hQspntL6</t>
+          <t>rX720WuH</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>vaZNtoqR</t>
+          <t>n5Eg2hB4</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
-        </is>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WdE2Z2y1</t>
+          <t>vuBo4Eth</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>dWZTBmVT</t>
-        </is>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vNHAXt6D</t>
+          <t>4Md3iycn</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>KdJMr7EE</t>
+          <t>EuWhpKkJ</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>nVS1TlC4</t>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>dWZTBmVT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>h2acepbK</t>
+          <t>Y1lKmgdB</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AsQgyP6l</t>
+          <t>UTsToXQN</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>vVQcGxl1</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Gp6AbAAT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stinat j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>OpNm82MB</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>figxD9PM</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pignard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>bJl87mmp</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ben el hadj salem h 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>YTLwacK1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>dYK8BH5F</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">letexier f 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>l8H0Dwy3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bastien b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>nRkUEVfA</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>QB1LGiQc</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brisard j 
+  fra </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0tIbS515</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>WWnG5RHd</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">leonard t 
+  fra </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>UapruDaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>b59ZhlYj</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bollengier m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,15 +436,10 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>referee</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -459,13 +454,12 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
         <is>
           <t>tAufB9Mi</t>
         </is>
@@ -480,13 +474,12 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>K6b7RoBp</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
         <is>
           <t>OpNm82MB</t>
         </is>
@@ -501,13 +494,12 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
         <is>
           <t>nVS1TlC4</t>
         </is>
@@ -522,13 +514,12 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>25Wk0Fko</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>CWxpUrtf</t>
         </is>
@@ -543,13 +534,12 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6FKPxxgf</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
         <is>
           <t>YTLwacK1</t>
         </is>
@@ -564,13 +554,12 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
-        <is>
-          <t>EgvyJSJo</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
         <is>
           <t>0tIbS515</t>
         </is>
@@ -585,13 +574,12 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>YHU1oFVQ</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
         <is>
           <t>dWZTBmVT</t>
         </is>
@@ -606,13 +594,12 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>pCcFFE7M</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
         <is>
           <t>UapruDaf</t>
         </is>
@@ -627,249 +614,14 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>4fMAHvLm</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
           <t>8MdrBIUb</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Gp6AbAAT</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stinat j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>OpNm82MB</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>figxD9PM</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pignard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CWxpUrtf</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>bJl87mmp</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ben el hadj salem h 
-  fra </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>K6b7RoBp</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>YTLwacK1</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>dYK8BH5F</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">letexier f 
-  fra </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>6FKPxxgf</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>l8H0Dwy3</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bastien b 
-  fra </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>d0X3cO3I</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>nRkUEVfA</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brisard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>QB1LGiQc</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brisard j 
-  fra </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>EgvyJSJo</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0tIbS515</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>WWnG5RHd</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">leonard t 
-  fra </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>pCcFFE7M</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>UapruDaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>b59ZhlYj</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bollengier m 
-  fra </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>YHU1oFVQ</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>tAufB9Mi</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0ljCkFRb</t>
+          <t>Gp6AbAAT</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -456,19 +456,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>d0X3cO3I</t>
+          <t>YTLwacK1</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>tAufB9Mi</t>
+          <t>pCcFFE7M</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bqYbtBlo</t>
+          <t>figxD9PM</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -476,19 +476,19 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>K6b7RoBp</t>
+          <t>tAufB9Mi</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>OpNm82MB</t>
+          <t>6FKPxxgf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>rX720WuH</t>
+          <t>bJl87mmp</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -496,19 +496,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>pYizckpN</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>nVS1TlC4</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>n5Eg2hB4</t>
+          <t>dYK8BH5F</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -516,19 +516,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>25Wk0Fko</t>
+          <t>CWxpUrtf</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CWxpUrtf</t>
+          <t>K6b7RoBp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>vuBo4Eth</t>
+          <t>l8H0Dwy3</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -536,19 +536,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6FKPxxgf</t>
+          <t>0tIbS515</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>YTLwacK1</t>
+          <t>YHU1oFVQ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>4Md3iycn</t>
+          <t>nRkUEVfA</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -556,19 +556,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EgvyJSJo</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0tIbS515</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EuWhpKkJ</t>
+          <t>QB1LGiQc</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -576,19 +576,19 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>YHU1oFVQ</t>
+          <t>dWZTBmVT</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>dWZTBmVT</t>
+          <t>d0X3cO3I</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Y1lKmgdB</t>
+          <t>WWnG5RHd</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -596,19 +596,19 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>pCcFFE7M</t>
+          <t>OpNm82MB</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>UapruDaf</t>
+          <t>25Wk0Fko</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>UTsToXQN</t>
+          <t>b59ZhlYj</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -616,12 +616,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>nVS1TlC4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>4fMAHvLm</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>8MdrBIUb</t>
         </is>
       </c>
     </row>

--- a/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/data/france/p6_deployment/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,10 +436,15 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -454,12 +459,13 @@
       <c r="B2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
         <is>
           <t>YTLwacK1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>pCcFFE7M</t>
         </is>
@@ -474,12 +480,13 @@
       <c r="B3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
         <is>
           <t>tAufB9Mi</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>6FKPxxgf</t>
         </is>
@@ -494,12 +501,13 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
         <is>
           <t>8MdrBIUb</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>pYizckpN</t>
         </is>
@@ -514,12 +522,13 @@
       <c r="B5" t="n">
         <v>1</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
         <is>
           <t>CWxpUrtf</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>K6b7RoBp</t>
         </is>
@@ -534,12 +543,13 @@
       <c r="B6" t="n">
         <v>1</v>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
         <is>
           <t>0tIbS515</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>YHU1oFVQ</t>
         </is>
@@ -554,12 +564,13 @@
       <c r="B7" t="n">
         <v>1</v>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
         <is>
           <t>dWZTBmVT</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>25Wk0Fko</t>
         </is>
@@ -574,12 +585,13 @@
       <c r="B8" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
         <is>
           <t>dWZTBmVT</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>d0X3cO3I</t>
         </is>
@@ -594,12 +606,13 @@
       <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
         <is>
           <t>OpNm82MB</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>25Wk0Fko</t>
         </is>
@@ -614,14 +627,119 @@
       <c r="B10" t="n">
         <v>1</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
         <is>
           <t>nVS1TlC4</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>4fMAHvLm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>xdpX3Q36</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">turpin c 
+  fra </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CWxpUrtf</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>d0X3cO3I</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Im9H9ezS</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vernice m 
+  fra </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>25Wk0Fko</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SMfm4Zck</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dechepy b 
+  fra </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>8MdrBIUb</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>pYizckpN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GryrQGK8</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">frappart s 
+  fra </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>tAufB9Mi</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EgvyJSJo</t>
         </is>
       </c>
     </row>
